--- a/AAAGameData/DataTables/ArrowLocalizationMoney.xlsx
+++ b/AAAGameData/DataTables/ArrowLocalizationMoney.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -99,87 +104,6 @@
   </si>
   <si>
     <t>PayPal,CashApp,GooglePlay,amazon,VISA,PagBank</t>
-  </si>
-  <si>
-    <t>巴西</t>
-  </si>
-  <si>
-    <t>PortugueseBrazil</t>
-  </si>
-  <si>
-    <t>巴西雷亚尔</t>
-  </si>
-  <si>
-    <t>R$</t>
-  </si>
-  <si>
-    <t>Pix,NUbank,PicPay</t>
-  </si>
-  <si>
-    <t>欧洲（法国）</t>
-  </si>
-  <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>欧元</t>
-  </si>
-  <si>
-    <t>€</t>
-  </si>
-  <si>
-    <t>PayPal,PayPay,Paytm,YandexMoney,OVO</t>
-  </si>
-  <si>
-    <t>俄罗斯</t>
-  </si>
-  <si>
-    <t>Russian</t>
-  </si>
-  <si>
-    <t>俄罗斯卢布</t>
-  </si>
-  <si>
-    <t>RUB</t>
-  </si>
-  <si>
-    <t>Qiwi-Wallet,YandexMoney</t>
-  </si>
-  <si>
-    <t>日本</t>
-  </si>
-  <si>
-    <t>Japanese</t>
-  </si>
-  <si>
-    <t>日元</t>
-  </si>
-  <si>
-    <t>￥</t>
-  </si>
-  <si>
-    <t>PayPal,Line-Pay</t>
-  </si>
-  <si>
-    <t>墨西哥</t>
-  </si>
-  <si>
-    <t>Spanish</t>
-  </si>
-  <si>
-    <t>墨西哥元</t>
-  </si>
-  <si>
-    <t>MX$</t>
-  </si>
-  <si>
-    <t>PayPal,PayPay,Pay,Paytm,YandexMoney,OVO</t>
-  </si>
-  <si>
-    <t>葡萄牙</t>
-  </si>
-  <si>
-    <t>PortuguesePortugal</t>
   </si>
 </sst>
 </file>
@@ -809,7 +733,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -818,10 +742,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1355,8 +1275,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="23.8571428571429" customWidth="1"/>
     <col min="3" max="4" width="24.5714285714286" customWidth="1"/>
@@ -1474,162 +1394,6 @@
       </c>
       <c r="I5" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="2">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="2">
-        <v>60</v>
-      </c>
-      <c r="H8" s="2">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9">
-        <v>140</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="2">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
